--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132182521</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132183271</v>
       </c>
       <c r="B3" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132182986</v>
       </c>
       <c r="B4" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132183511</v>
       </c>
       <c r="B5" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132183517</v>
       </c>
       <c r="B6" t="n">
-        <v>92188</v>
+        <v>92191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132183383</v>
+        <v>132183449</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,19 +1221,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502328</v>
+        <v>502314</v>
       </c>
       <c r="R7" t="n">
-        <v>6714066</v>
+        <v>6714075</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132183449</v>
+        <v>132183383</v>
       </c>
       <c r="B8" t="n">
-        <v>91889</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,23 +1328,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502314</v>
+        <v>502328</v>
       </c>
       <c r="R8" t="n">
-        <v>6714075</v>
+        <v>6714066</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,7 +1423,7 @@
         <v>132183498</v>
       </c>
       <c r="B9" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>132182965</v>
       </c>
       <c r="B10" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132183449</v>
+        <v>132183383</v>
       </c>
       <c r="B7" t="n">
-        <v>91892</v>
+        <v>91912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,23 +1221,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1245,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502314</v>
+        <v>502328</v>
       </c>
       <c r="R7" t="n">
-        <v>6714075</v>
+        <v>6714066</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132183383</v>
+        <v>132183449</v>
       </c>
       <c r="B8" t="n">
-        <v>91912</v>
+        <v>91892</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,19 +1324,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502328</v>
+        <v>502314</v>
       </c>
       <c r="R8" t="n">
-        <v>6714066</v>
+        <v>6714075</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132183383</v>
+        <v>132183449</v>
       </c>
       <c r="B7" t="n">
-        <v>91912</v>
+        <v>91892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,19 +1221,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502328</v>
+        <v>502314</v>
       </c>
       <c r="R7" t="n">
-        <v>6714066</v>
+        <v>6714075</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132183449</v>
+        <v>132183383</v>
       </c>
       <c r="B8" t="n">
-        <v>91892</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,23 +1328,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502314</v>
+        <v>502328</v>
       </c>
       <c r="R8" t="n">
-        <v>6714075</v>
+        <v>6714066</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132182521</v>
       </c>
       <c r="B2" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132183271</v>
       </c>
       <c r="B3" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132182986</v>
       </c>
       <c r="B4" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132183511</v>
       </c>
       <c r="B5" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132183517</v>
       </c>
       <c r="B6" t="n">
-        <v>92191</v>
+        <v>92197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132183383</v>
+        <v>132183449</v>
       </c>
       <c r="B7" t="n">
-        <v>91912</v>
+        <v>91898</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,19 +1221,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502328</v>
+        <v>502314</v>
       </c>
       <c r="R7" t="n">
-        <v>6714066</v>
+        <v>6714075</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132183449</v>
+        <v>132183383</v>
       </c>
       <c r="B8" t="n">
-        <v>91892</v>
+        <v>91918</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1324,23 +1328,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502314</v>
+        <v>502328</v>
       </c>
       <c r="R8" t="n">
-        <v>6714075</v>
+        <v>6714066</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,7 +1423,7 @@
         <v>132183498</v>
       </c>
       <c r="B9" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>132182965</v>
       </c>
       <c r="B10" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132182521</v>
       </c>
       <c r="B2" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132183271</v>
       </c>
       <c r="B3" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132182986</v>
       </c>
       <c r="B4" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132183511</v>
       </c>
       <c r="B5" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132183517</v>
       </c>
       <c r="B6" t="n">
-        <v>92197</v>
+        <v>92207</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>132183449</v>
       </c>
       <c r="B7" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>132183383</v>
       </c>
       <c r="B8" t="n">
-        <v>91918</v>
+        <v>91928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1423,7 +1423,7 @@
         <v>132183498</v>
       </c>
       <c r="B9" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>132182965</v>
       </c>
       <c r="B10" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132182521</v>
       </c>
       <c r="B2" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>132183271</v>
       </c>
       <c r="B3" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>132182986</v>
       </c>
       <c r="B4" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>132183511</v>
       </c>
       <c r="B5" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>132183517</v>
       </c>
       <c r="B6" t="n">
-        <v>92207</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132183449</v>
+        <v>132183383</v>
       </c>
       <c r="B7" t="n">
-        <v>91908</v>
+        <v>91929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,23 +1221,19 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1245,10 +1241,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502314</v>
+        <v>502328</v>
       </c>
       <c r="R7" t="n">
-        <v>6714075</v>
+        <v>6714066</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1280,7 +1276,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1286,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1313,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132183383</v>
+        <v>132183449</v>
       </c>
       <c r="B8" t="n">
-        <v>91928</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,19 +1324,23 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1348,10 +1348,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502328</v>
+        <v>502314</v>
       </c>
       <c r="R8" t="n">
-        <v>6714066</v>
+        <v>6714075</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,7 +1423,7 @@
         <v>132183498</v>
       </c>
       <c r="B9" t="n">
-        <v>99116</v>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1549,7 +1549,7 @@
         <v>132182965</v>
       </c>
       <c r="B10" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132182521</v>
+        <v>132183517</v>
       </c>
       <c r="B2" t="n">
-        <v>91913</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502276</v>
+        <v>502309</v>
       </c>
       <c r="R2" t="n">
-        <v>6714052</v>
+        <v>6714163</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132183271</v>
+        <v>132182521</v>
       </c>
       <c r="B3" t="n">
-        <v>91913</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502279</v>
+        <v>502276</v>
       </c>
       <c r="R3" t="n">
-        <v>6714060</v>
+        <v>6714052</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,32 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132182986</v>
+        <v>132182586</v>
       </c>
       <c r="B4" t="n">
-        <v>99122</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502279</v>
+        <v>502291</v>
       </c>
       <c r="R4" t="n">
-        <v>6714118</v>
+        <v>6714003</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,32 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132183511</v>
+        <v>132183271</v>
       </c>
       <c r="B5" t="n">
-        <v>99122</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502309</v>
+        <v>502279</v>
       </c>
       <c r="R5" t="n">
-        <v>6714167</v>
+        <v>6714060</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132183517</v>
+        <v>132183449</v>
       </c>
       <c r="B6" t="n">
-        <v>92212</v>
+        <v>91974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502309</v>
+        <v>502314</v>
       </c>
       <c r="R6" t="n">
-        <v>6714163</v>
+        <v>6714075</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,30 +1210,34 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132183383</v>
+        <v>132182965</v>
       </c>
       <c r="B7" t="n">
-        <v>91933</v>
+        <v>91937</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1241,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502328</v>
+        <v>502292</v>
       </c>
       <c r="R7" t="n">
-        <v>6714066</v>
+        <v>6714085</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1276,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1286,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132183449</v>
+        <v>132182248</v>
       </c>
       <c r="B8" t="n">
-        <v>91913</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1348,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502314</v>
+        <v>502359</v>
       </c>
       <c r="R8" t="n">
-        <v>6714075</v>
+        <v>6714237</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1383,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1393,7 +1397,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1420,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132183498</v>
+        <v>132182812</v>
       </c>
       <c r="B9" t="n">
-        <v>99122</v>
+        <v>99195</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,12 +1459,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1469,10 +1478,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502318</v>
+        <v>502226</v>
       </c>
       <c r="R9" t="n">
-        <v>6714139</v>
+        <v>6714094</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1504,7 +1513,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,12 +1523,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:40</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1546,32 +1550,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132182965</v>
+        <v>132182986</v>
       </c>
       <c r="B10" t="n">
-        <v>91876</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1581,10 +1585,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502292</v>
+        <v>502279</v>
       </c>
       <c r="R10" t="n">
-        <v>6714085</v>
+        <v>6714118</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1616,7 +1620,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1626,7 +1630,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,6 +1654,239 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>132183498</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sarbergstjärnen, Sarbergstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>502318</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6714139</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>132183511</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sarbergstjärnen, Sarbergstjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>502309</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6714167</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Gagnef</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-04-04</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14556-2026 artfynd.xlsx
+++ b/artfynd/A 14556-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132183517</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132182521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132182586</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132183271</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132183449</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132182965</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132182248</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1547,6 +1587,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132182812</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1654,6 +1699,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132182986</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1780,6 +1830,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132183498</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,8 +1942,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132183511</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>